--- a/data/isx_xlsx/SYN.IC.xlsx
+++ b/data/isx_xlsx/SYN.IC.xlsx
@@ -8867,9 +8867,18 @@
       <c r="P39" s="15">
         <v>221.15</v>
       </c>
-      <c r="Q39" s="18"/>
-      <c r="R39" s="18"/>
-      <c r="S39" s="18"/>
+      <c r="Q39" s="19">
+        <f t="shared" ref="Q39:S39" si="1">SUM(Q40:Q45,Q51)</f>
+        <v>244.03</v>
+      </c>
+      <c r="R39" s="19">
+        <f t="shared" si="1"/>
+        <v>242.85</v>
+      </c>
+      <c r="S39" s="19">
+        <f t="shared" si="1"/>
+        <v>320.21</v>
+      </c>
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
@@ -10208,8 +10217,12 @@
       <c r="P74" s="19">
         <v>36.97</v>
       </c>
-      <c r="Q74" s="18"/>
-      <c r="R74" s="18"/>
+      <c r="Q74" s="19">
+        <v>38.52</v>
+      </c>
+      <c r="R74" s="19">
+        <v>9.27</v>
+      </c>
       <c r="S74" s="15">
         <v>538.15</v>
       </c>
